--- a/data/trans_camb/IMC_inf_MED_R3-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IMC_inf_MED_R3-Estudios-trans_camb.xlsx
@@ -601,22 +601,22 @@
         </is>
       </c>
       <c r="C4" s="5" t="n">
-        <v>-3.300640151113282</v>
+        <v>-4.030837273672502</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>-9.008012252790982</v>
+        <v>-6.564484684295499</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>1.296300216951682</v>
+        <v>-0.9738060427568307</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>-11.86808242008897</v>
+        <v>-3.665019547839962</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.7583878067338706</v>
+        <v>-2.289965844962408</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>-9.451718518989299</v>
+        <v>-4.893654164137439</v>
       </c>
     </row>
     <row r="5">
@@ -627,22 +627,22 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>-17.84786774197174</v>
+        <v>-15.39054126480348</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>-24.10273204261241</v>
+        <v>-20.80245984415168</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>-11.63948225433826</v>
+        <v>-11.82398388236502</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>-22.50012290209301</v>
+        <v>-17.0649561030122</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-10.7524366254715</v>
+        <v>-10.19730608687338</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>-19.40461376507855</v>
+        <v>-14.9179971827704</v>
       </c>
     </row>
     <row r="6">
@@ -653,22 +653,22 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>10.83249920221226</v>
+        <v>8.673370642275533</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>10.93861625566687</v>
+        <v>12.29677601735998</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>15.873509036872</v>
+        <v>10.72372887554575</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>5.933881095271247</v>
+        <v>14.14680006266654</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>8.373623589096962</v>
+        <v>6.446400103806516</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>2.564521857052235</v>
+        <v>8.327958170749474</v>
       </c>
     </row>
     <row r="7">
@@ -679,22 +679,22 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>-0.1223424960980053</v>
+        <v>-0.1642881905796679</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>-0.3338936247006953</v>
+        <v>-0.2675541674467689</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>0.05999989478750831</v>
+        <v>-0.0504857523055821</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>-0.549320047333879</v>
+        <v>-0.1900083394056007</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>-0.03147515665343192</v>
+        <v>-0.1048930185279168</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>-0.3922720254569267</v>
+        <v>-0.2241562502066542</v>
       </c>
     </row>
     <row r="8">
@@ -705,22 +705,22 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>-0.5422761303081127</v>
+        <v>-0.5120463335905671</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>-0.7483804711853664</v>
+        <v>-0.7716776914005371</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>-0.4557333554892312</v>
+        <v>-0.4997187889767088</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>-0.9100745635716642</v>
+        <v>-0.7549109227591957</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>-0.389394330481612</v>
+        <v>-0.3995440553980983</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.725249517447669</v>
+        <v>-0.6167570170440877</v>
       </c>
     </row>
     <row r="9">
@@ -731,22 +731,22 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0.5447687969300562</v>
+        <v>0.5108288760896516</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0.5350424330216758</v>
+        <v>0.6329461514896352</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>0.9348511534591792</v>
+        <v>0.7727321384049484</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.458239854315773</v>
+        <v>0.932146314287626</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.4443782381194245</v>
+        <v>0.367702923947993</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>0.1598432326952276</v>
+        <v>0.4440370325428571</v>
       </c>
     </row>
     <row r="10">
@@ -761,22 +761,22 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>-6.697883227460924</v>
+        <v>-4.899473839213952</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>-6.120501252714686</v>
+        <v>-4.851002685722161</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-10.0833480718774</v>
+        <v>-10.69971137964952</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>-9.857066421787996</v>
+        <v>-9.785861772186152</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-8.401305543318029</v>
+        <v>-7.711912894456358</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>-7.406785903520899</v>
+        <v>-6.742952264790741</v>
       </c>
     </row>
     <row r="11">
@@ -787,22 +787,22 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>-11.99554487872775</v>
+        <v>-9.897362826381222</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>-12.46798489754934</v>
+        <v>-11.06771215933157</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>-15.10734133790412</v>
+        <v>-15.2227173579339</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>-15.5170511775537</v>
+        <v>-14.86161019790607</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-12.12496900644289</v>
+        <v>-11.20091208686499</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>-11.66507145767838</v>
+        <v>-10.8292167489017</v>
       </c>
     </row>
     <row r="12">
@@ -813,22 +813,22 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>-1.161133853742768</v>
+        <v>0.2017663834814583</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.817358859567326</v>
+        <v>1.592963842429994</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>-5.246159254750675</v>
+        <v>-6.392769939027422</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>-3.848665283279282</v>
+        <v>-3.96001010008119</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-5.018517827464737</v>
+        <v>-4.338013784415367</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>-2.926747424782655</v>
+        <v>-2.099913765465965</v>
       </c>
     </row>
     <row r="13">
@@ -839,22 +839,22 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>-0.2257335806477668</v>
+        <v>-0.1782382777070963</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>-0.2062745222953334</v>
+        <v>-0.1764749424591956</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>-0.4403078211640996</v>
+        <v>-0.4762147598361604</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>-0.4304268193767903</v>
+        <v>-0.435541824286492</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>-0.3177717641088877</v>
+        <v>-0.3073961528333842</v>
       </c>
       <c r="H13" s="6" t="n">
-        <v>-0.2801549605359449</v>
+        <v>-0.2687734694754932</v>
       </c>
     </row>
     <row r="14">
@@ -865,22 +865,22 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>-0.3694229692716999</v>
+        <v>-0.3325777457955136</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>-0.3921122380364849</v>
+        <v>-0.3717960448512836</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>-0.5802443237239192</v>
+        <v>-0.6108247057361799</v>
       </c>
       <c r="F14" s="6" t="n">
-        <v>-0.6371345690993765</v>
+        <v>-0.6135579418928643</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>-0.4185851236928367</v>
+        <v>-0.4164874883568492</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>-0.4209625759515555</v>
+        <v>-0.4151571327729806</v>
       </c>
     </row>
     <row r="15">
@@ -891,22 +891,22 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>-0.0447143066475625</v>
+        <v>0.006735280189268509</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0.0336069546347893</v>
+        <v>0.0681904979075343</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>-0.2414383903206933</v>
+        <v>-0.3176226861643043</v>
       </c>
       <c r="F15" s="6" t="n">
-        <v>-0.1873340081298456</v>
+        <v>-0.1763481206498173</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>-0.1941559650353383</v>
+        <v>-0.1838478860578785</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>-0.1175989957733754</v>
+        <v>-0.09123803454676138</v>
       </c>
     </row>
     <row r="16">
@@ -921,22 +921,22 @@
         </is>
       </c>
       <c r="C16" s="5" t="n">
-        <v>-8.011520770764349</v>
+        <v>-8.27551695946965</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>-13.65201116605765</v>
+        <v>-12.00745532371215</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-4.860817817684246</v>
+        <v>-4.33708989123946</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-9.730206046941676</v>
+        <v>-9.030709843035975</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-6.418270333765966</v>
+        <v>-6.30677871641892</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-11.69248175244188</v>
+        <v>-10.50107218862746</v>
       </c>
     </row>
     <row r="17">
@@ -947,22 +947,22 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>-15.91995785495289</v>
+        <v>-16.06854638870613</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>-22.31644361715962</v>
+        <v>-19.69615435977681</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-12.92123221033231</v>
+        <v>-11.88086379964811</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>-16.97902023085555</v>
+        <v>-17.37046102064524</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-12.13950480504465</v>
+        <v>-10.95511424682771</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-17.45680900060475</v>
+        <v>-16.08823227618084</v>
       </c>
     </row>
     <row r="18">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="C18" s="5" t="n">
-        <v>1.012911637352659</v>
+        <v>-1.280195637337035</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>-5.040183724667648</v>
+        <v>-3.230343152379196</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>3.742110512289726</v>
+        <v>2.987227452361377</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>-0.9489077136382198</v>
+        <v>-1.591127021339827</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.2837321960091273</v>
+        <v>-0.1618153834421281</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-5.521134747492259</v>
+        <v>-4.561857557877753</v>
       </c>
     </row>
     <row r="19">
@@ -999,22 +999,22 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>-0.3325601367351097</v>
+        <v>-0.3792990464714036</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>-0.5666982374508931</v>
+        <v>-0.5503482594667867</v>
       </c>
       <c r="E19" s="6" t="n">
-        <v>-0.2557533033542747</v>
+        <v>-0.23951151574273</v>
       </c>
       <c r="F19" s="6" t="n">
-        <v>-0.5119575413358405</v>
+        <v>-0.498712052776984</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>-0.2976874269678024</v>
+        <v>-0.3159826306861583</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>-0.5423119667366948</v>
+        <v>-0.5261253905340531</v>
       </c>
     </row>
     <row r="20">
@@ -1025,22 +1025,22 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>-0.5629270550223276</v>
+        <v>-0.6153607553319176</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>-0.7844458394918569</v>
+        <v>-0.7617146050298009</v>
       </c>
       <c r="E20" s="6" t="n">
-        <v>-0.5454529637416518</v>
+        <v>-0.5418019039371439</v>
       </c>
       <c r="F20" s="6" t="n">
-        <v>-0.7512946254651998</v>
+        <v>-0.7647480879748818</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>-0.5074869182152588</v>
+        <v>-0.492017725030833</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>-0.719261615427763</v>
+        <v>-0.7087026908413302</v>
       </c>
     </row>
     <row r="21">
@@ -1051,22 +1051,22 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>0.06688849045685386</v>
+        <v>-0.0678173956082002</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>-0.1913756320745432</v>
+        <v>-0.1408291633052895</v>
       </c>
       <c r="E21" s="6" t="n">
-        <v>0.2606996148627451</v>
+        <v>0.2175914222662956</v>
       </c>
       <c r="F21" s="6" t="n">
-        <v>-0.02878161715274289</v>
+        <v>-0.04544115498510382</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>-0.01799866784014445</v>
+        <v>-0.01858937435865175</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>-0.2944952281901566</v>
+        <v>-0.2508319314985637</v>
       </c>
     </row>
     <row r="22">
@@ -1081,22 +1081,22 @@
         </is>
       </c>
       <c r="C22" s="5" t="n">
-        <v>-6.632688235448433</v>
+        <v>-5.609659174776308</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>-8.148202494863172</v>
+        <v>-6.712070643750661</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-7.893069262130526</v>
+        <v>-8.197869741194271</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-10.08718235704703</v>
+        <v>-9.119963726172402</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-7.192042686080646</v>
+        <v>-6.795243007295642</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>-8.72317335866507</v>
+        <v>-7.57181121582633</v>
       </c>
     </row>
     <row r="23">
@@ -1107,22 +1107,22 @@
         </is>
       </c>
       <c r="C23" s="5" t="n">
-        <v>-11.03929236754414</v>
+        <v>-9.394689042973919</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>-13.05082649018452</v>
+        <v>-11.31685080565764</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>-11.27482969603891</v>
+        <v>-11.71637426954293</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>-14.23032333258939</v>
+        <v>-13.0235595390953</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-10.12679572802875</v>
+        <v>-9.651448659455442</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>-12.11980125205647</v>
+        <v>-10.80742861453692</v>
       </c>
     </row>
     <row r="24">
@@ -1133,22 +1133,22 @@
         </is>
       </c>
       <c r="C24" s="5" t="n">
-        <v>-2.292604322882021</v>
+        <v>-1.648235650130232</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>-2.17190640022175</v>
+        <v>-1.328502553211405</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>-3.426379899764664</v>
+        <v>-4.734638920651528</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>-5.222438029456126</v>
+        <v>-4.197196437668403</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-4.310517152311587</v>
+        <v>-4.198982401520034</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>-5.119882155419949</v>
+        <v>-3.951049263276195</v>
       </c>
     </row>
     <row r="25">
@@ -1159,22 +1159,22 @@
         </is>
       </c>
       <c r="C25" s="6" t="n">
-        <v>-0.2359887764218249</v>
+        <v>-0.2167902600893522</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>-0.289910254868178</v>
+        <v>-0.2593939302301438</v>
       </c>
       <c r="E25" s="6" t="n">
-        <v>-0.3618655677473216</v>
+        <v>-0.3899495765883395</v>
       </c>
       <c r="F25" s="6" t="n">
-        <v>-0.4624568528894819</v>
+        <v>-0.4338109906347273</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>-0.2873773900851836</v>
+        <v>-0.2890716631494556</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>-0.3485578301593611</v>
+        <v>-0.3221071062304381</v>
       </c>
     </row>
     <row r="26">
@@ -1185,22 +1185,22 @@
         </is>
       </c>
       <c r="C26" s="6" t="n">
-        <v>-0.3614972912058264</v>
+        <v>-0.3413640972846075</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>-0.437919244821275</v>
+        <v>-0.4100183511158397</v>
       </c>
       <c r="E26" s="6" t="n">
-        <v>-0.4813608701542939</v>
+        <v>-0.5075838240134847</v>
       </c>
       <c r="F26" s="6" t="n">
-        <v>-0.6049546350922773</v>
+        <v>-0.5861566757789561</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>-0.3790480912832851</v>
+        <v>-0.380369588739435</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>-0.4608577140072387</v>
+        <v>-0.4372417862048654</v>
       </c>
     </row>
     <row r="27">
@@ -1211,22 +1211,22 @@
         </is>
       </c>
       <c r="C27" s="6" t="n">
-        <v>-0.08960643952947669</v>
+        <v>-0.07184589181948922</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>-0.07653176795831677</v>
+        <v>-0.05328496975897574</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>-0.1825640570666804</v>
+        <v>-0.2474241005013212</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>-0.2372720119698102</v>
+        <v>-0.2227324448853839</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>-0.1792305371069027</v>
+        <v>-0.1868051511698236</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>-0.2155577375233511</v>
+        <v>-0.1688252362483865</v>
       </c>
     </row>
     <row r="28">
